--- a/wwescorecard.xlsx
+++ b/wwescorecard.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="75">
   <si>
     <t>Event #</t>
   </si>
@@ -124,10 +124,10 @@
     <t>Allegiant Stadium, Las Vegas</t>
   </si>
   <si>
-    <t>Benchmark International Arena, Tampa</t>
-  </si>
-  <si>
-    <t>Unipol Arena, Bologna</t>
+    <t>Coliseo de Puerto Rico, San Juan</t>
+  </si>
+  <si>
+    <t>Inalpi Arena, Turin</t>
   </si>
   <si>
     <t>U.S. Bank Stadium, Minneapolis</t>
@@ -139,7 +139,7 @@
     <t>~400 (est.)</t>
   </si>
   <si>
-    <t>~14,000 (est.)</t>
+    <t>11,425</t>
   </si>
   <si>
     <t>~25,000 (est.)</t>
@@ -148,34 +148,34 @@
     <t>14,895</t>
   </si>
   <si>
-    <t>47,093 (stadium authority); 106,072 combined (WWE announced)</t>
-  </si>
-  <si>
-    <t>50,033 (stadium authority); 106,072 combined (WWE announced)</t>
-  </si>
-  <si>
-    <t>~12,000–14,000 (est.)</t>
-  </si>
-  <si>
-    <t>~10,000–12,000 (est.)</t>
+    <t>47,093 (stadium authority)</t>
+  </si>
+  <si>
+    <t>50,033 (stadium authority)</t>
+  </si>
+  <si>
+    <t>14,220 (WrestleTix)</t>
+  </si>
+  <si>
+    <t>~12,000 (sold out)</t>
   </si>
   <si>
     <t>18,000+ (sold out)</t>
   </si>
   <si>
-    <t>35,759 (WrestleTix)</t>
-  </si>
-  <si>
-    <t>33,086 (WrestleTix)</t>
-  </si>
-  <si>
-    <t>10,834 tickets sold (as of Sep 15)</t>
+    <t>35,654 (WrestleTix)</t>
+  </si>
+  <si>
+    <t>32,293 (WrestleTix)</t>
+  </si>
+  <si>
+    <t>10,834 (tickets sold)</t>
   </si>
   <si>
     <t>Not applicable (NXT)</t>
   </si>
   <si>
-    <t>~$1.4M–$2.1M (est.)</t>
+    <t>~$1.1M–$1.6M (est.)</t>
   </si>
   <si>
     <t>Not applicable (Saudi-funded)</t>
@@ -184,49 +184,61 @@
     <t>~$2.2M–$3.0M (est.)</t>
   </si>
   <si>
-    <t>Not disclosed</t>
+    <t>~$27M–$30M (est.)</t>
+  </si>
+  <si>
+    <t>~$29M–$32M (est.)</t>
   </si>
   <si>
     <t>~$1.5M–$2.0M (est.)</t>
   </si>
   <si>
-    <t>~$1.0M–$1.5M (est.)</t>
-  </si>
-  <si>
-    <t>~$4.5M–$6.5M (est.)</t>
-  </si>
-  <si>
-    <t>~$4.2M–$6.0M (est.)</t>
-  </si>
-  <si>
-    <t>~$800K–$1.2M (est.)</t>
+    <t>~$1.3M–$1.8M (est.)</t>
+  </si>
+  <si>
+    <t>~$4.8M–$7.0M (est.)</t>
+  </si>
+  <si>
+    <t>~$4.4M–$6.5M (est.)</t>
+  </si>
+  <si>
+    <t>~$750K–$1.1M (est.)</t>
   </si>
   <si>
     <t>~200K (est.)</t>
   </si>
   <si>
+    <t>~1.5M (est.)</t>
+  </si>
+  <si>
     <t>3.1M (Netflix, ex-US)</t>
   </si>
   <si>
     <t>1.9M (Netflix, ex-US)</t>
   </si>
   <si>
-    <t>2.7M (Netflix, ex-US); most-viewed ESPN2 telecast of 2026</t>
-  </si>
-  <si>
-    <t>3.0M (Netflix, ex-US); most-viewed ESPN telecast of weekend</t>
-  </si>
-  <si>
-    <t>1.4M (Netflix, ex-US); 998K first hour on ESPN2</t>
+    <t>2.7M (Netflix, ex-US)</t>
+  </si>
+  <si>
+    <t>3.0M (Netflix, ex-US)</t>
+  </si>
+  <si>
+    <t>1.4M (Netflix, ex-US)</t>
   </si>
   <si>
     <t>1.6M (Netflix, ex-US)</t>
   </si>
   <si>
-    <t>1.0M (Netflix, ex-US, partial tracking); 186.8M social video views</t>
-  </si>
-  <si>
-    <t>Not yet reported</t>
+    <t>1.0M (Netflix, ex-US, partial)</t>
+  </si>
+  <si>
+    <t>~1.3M–1.6M (est.)</t>
+  </si>
+  <si>
+    <t>~1.2M–1.5M (est.)</t>
+  </si>
+  <si>
+    <t>~500K–1M (est.)</t>
   </si>
 </sst>
 </file>
@@ -630,7 +642,7 @@
         <v>52</v>
       </c>
       <c r="G2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -653,7 +665,7 @@
         <v>53</v>
       </c>
       <c r="G3" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -676,7 +688,7 @@
         <v>54</v>
       </c>
       <c r="G4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -699,7 +711,7 @@
         <v>55</v>
       </c>
       <c r="G5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -722,7 +734,7 @@
         <v>56</v>
       </c>
       <c r="G6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -742,10 +754,10 @@
         <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -765,10 +777,10 @@
         <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -788,10 +800,10 @@
         <v>47</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -814,7 +826,7 @@
         <v>54</v>
       </c>
       <c r="G10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -834,10 +846,10 @@
         <v>49</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -857,10 +869,10 @@
         <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -880,10 +892,10 @@
         <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G13" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
